--- a/sheets/real-estate/duplex-house-hack/duplex-house-hack.xlsx
+++ b/sheets/real-estate/duplex-house-hack/duplex-house-hack.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\000_drive_drive\600_PROJECTS\modelstack\sheets\real-estate\duplex-house-hack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4D6646-30AD-421D-8131-9DF0711745BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF50404-92F9-4A72-A7C0-7D624C9F16FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="77">
   <si>
     <t>Property Type</t>
   </si>
@@ -246,18 +246,6 @@
     <t>Monthly Impact</t>
   </si>
   <si>
-    <t>Rate +1%</t>
-  </si>
-  <si>
-    <t>Tenant Rent -10%</t>
-  </si>
-  <si>
-    <t>Tax +15%</t>
-  </si>
-  <si>
-    <t>Maintenance +20%</t>
-  </si>
-  <si>
     <t>Purchase price</t>
   </si>
   <si>
@@ -273,7 +261,13 @@
     <t>Worst-case housing cost</t>
   </si>
   <si>
-    <t>math</t>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Tenant Rent</t>
+  </si>
+  <si>
+    <t>Overview</t>
   </si>
 </sst>
 </file>
@@ -284,7 +278,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,8 +318,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,6 +350,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F2E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -380,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -418,17 +424,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -579,6 +584,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-8C19-40D0-9028-852BD6B67549}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -619,6 +629,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-8C19-40D0-9028-852BD6B67549}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -659,6 +674,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-8C19-40D0-9028-852BD6B67549}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -699,6 +719,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-8C19-40D0-9028-852BD6B67549}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -739,6 +764,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-8C19-40D0-9028-852BD6B67549}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -779,6 +809,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-8C19-40D0-9028-852BD6B67549}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -822,6 +857,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-8C19-40D0-9028-852BD6B67549}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -865,6 +905,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-8C19-40D0-9028-852BD6B67549}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -1154,22 +1199,61 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-934A-4228-B534-3D24D52BACC8}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Scenario Grid'!$I$15:$I$18</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>Rate +1%</c:v>
+                  <c:v>Rate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Tenant Rent -10%</c:v>
+                  <c:v>Tenant Rent</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Tax +15%</c:v>
+                  <c:v>Tax</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Maintenance +20%</c:v>
+                  <c:v>Maintenance</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1238,7 +1322,17 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1783,12 +1877,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>457199</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1190</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>29766</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4981575" cy="3324225"/>
+    <xdr:ext cx="4981575" cy="3275408"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -2137,7 +2231,7 @@
     <col min="1" max="1" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2149,9 +2243,9 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="13"/>
+        <v>76</v>
+      </c>
+      <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2164,7 +2258,7 @@
       <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <f>'Monthly Housing Cost'!D2</f>
         <v>2555.5</v>
       </c>
@@ -2180,7 +2274,7 @@
       <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <f>'Monthly Housing Cost'!L2</f>
         <v>1263.7994774236108</v>
       </c>
@@ -2197,7 +2291,7 @@
       <c r="D4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <f>'Monthly Housing Cost'!M2</f>
         <v>686.20052257638918</v>
       </c>
@@ -2210,10 +2304,10 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <f>IF('Unit Rent Roll'!B8=0,0,('Property &amp; Loan'!B7+'Property &amp; Loan'!B8+'Property &amp; Loan'!B9+'Property &amp; Loan'!B10+'Property &amp; Loan'!B11+'Property &amp; Loan'!B12+'Property &amp; Loan'!B13)/'Unit Rent Roll'!B8)</f>
         <v>1.4198139321277363</v>
       </c>
@@ -2227,7 +2321,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="13"/>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -2239,7 +2333,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="13"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -2250,7 +2344,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="13"/>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -2261,7 +2355,7 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="13"/>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -2272,7 +2366,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="13"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -2283,7 +2377,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="13"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -2294,7 +2388,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="13"/>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -2305,7 +2399,7 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="13"/>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2316,7 +2410,7 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="13"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -2327,7 +2421,7 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="13"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -2338,7 +2432,7 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="13"/>
+      <c r="E16" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2478,7 +2572,7 @@
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="14" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="1"/>
@@ -3579,7 +3673,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J15" s="5">
         <v>210</v>
@@ -3595,7 +3689,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J16" s="5">
         <v>275</v>
@@ -3611,7 +3705,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="3" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="J17" s="5">
         <v>64</v>
@@ -3627,7 +3721,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="3" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="J18" s="5">
         <v>35</v>
@@ -3662,7 +3756,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B1" s="7">
         <f>'Property &amp; Loan'!B2</f>
@@ -3671,7 +3765,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B2" s="7">
         <f>'Property &amp; Loan'!B4</f>
@@ -3680,7 +3774,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B3" s="7">
         <f>SUM('Property &amp; Loan'!B7:B13)</f>
@@ -3716,7 +3810,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B7" s="7">
         <f>AVERAGE('Monthly Housing Cost'!M2:M13)</f>
@@ -3725,7 +3819,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B8" s="7">
         <f>MAX('Scenario Grid'!C3:G7)</f>
